--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6023EB-ED12-4C5E-9D24-6C2F76F87146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42CD3A1-2D0E-4931-86C5-0398E1999C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42CD3A1-2D0E-4931-86C5-0398E1999C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED75086-FB41-42C3-83CA-19C1B6939D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED75086-FB41-42C3-83CA-19C1B6939D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DCD53DABFD093B5FF6B2B38070D9F781" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789003B0-7696-4793-BFC8-AA33F51ECACE}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer">'Opdateret d. 07-10-2026'!$A$1:$N$93</definedName>
+    <definedName name="Lægesystemer">'Opdateret d. 08-10-2026'!$A$1:$N$93</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DCD53DABFD093B5FF6B2B38070D9F781" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789003B0-7696-4793-BFC8-AA33F51ECACE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0AA0A2-FBF7-40D1-A9F2-C5EB4864D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer">'Opdateret d. 08-10-2026'!$A$1:$N$93</definedName>
+    <definedName name="Lægesystemer">'Opdateret d. 09-10-2026'!$A$1:$N$93</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0AA0A2-FBF7-40D1-A9F2-C5EB4864D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D6A9F6-214E-4A3A-BB69-812BAF22F8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer_excel.XLSX
+++ b/html/Lægesystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D6A9F6-214E-4A3A-BB69-812BAF22F8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9DCD53DABFD093BCF267384F871D9F781" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A3BB13-03CC-451A-A631-881780E1EBB3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer">'Opdateret d. 09-10-2026'!$A$1:$N$93</definedName>
+    <definedName name="Lægesystemer">'Opdateret d. 23-10-2026'!$A$1:$N$93</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
